--- a/data/trending_integrated_20261028_12.xlsx
+++ b/data/trending_integrated_20261028_12.xlsx
@@ -578,10 +578,10 @@
         <v>-0.19</v>
       </c>
       <c r="E2" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F2" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G2" t="n">
         <v>231</v>
@@ -610,7 +610,7 @@
         <v>1.39</v>
       </c>
       <c r="O2" t="n">
-        <v>149406142766</v>
+        <v>149729535316</v>
       </c>
       <c r="P2" t="n">
         <v>8100</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>미국 광통신주 급등에 따른 기대감 및 상한가 기록. 일부 부정적 인식 존재.</t>
+          <t>미국 광통신주 급등에 따른 기대감. 전고점 돌파 및 상승 가능성 언급.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['광통신', '상한가', '호재']</t>
+          <t>['광통신', '상승', '전고점']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -655,31 +655,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>원익홀딩스</t>
+          <t>멜콘</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>28400</v>
+        <v>18950</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+19.58%</t>
+          <t>'+19.71%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.15</v>
+        <v>1.02</v>
       </c>
       <c r="E3" t="n">
-        <v>63</v>
+        <v>140</v>
       </c>
       <c r="F3" t="n">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="G3" t="n">
-        <v>181</v>
+        <v>263</v>
       </c>
       <c r="H3" t="n">
-        <v>5.16</v>
+        <v>1.11</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,91 +687,91 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>23750</v>
+        <v>15830</v>
       </c>
       <c r="K3" t="n">
-        <v>24200</v>
+        <v>17170</v>
       </c>
       <c r="L3" t="n">
-        <v>29900</v>
+        <v>19055</v>
       </c>
       <c r="M3" t="n">
-        <v>24200</v>
+        <v>15830</v>
       </c>
       <c r="N3" t="n">
-        <v>5.31</v>
+        <v>0.09</v>
       </c>
       <c r="O3" t="n">
-        <v>145664378450</v>
+        <v>236304437150</v>
       </c>
       <c r="P3" t="n">
-        <v>50600</v>
+        <v>28800</v>
       </c>
       <c r="Q3" t="n">
-        <v>13210</v>
+        <v>11550</v>
       </c>
       <c r="R3" t="n">
-        <v>-35000</v>
+        <v>-21000</v>
       </c>
       <c r="S3" t="n">
-        <v>126000</v>
+        <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>원익홀딩스, 로봇 관련주로 주목받으며 기대감 형성. 다만, 구체적인 호재보다는 기대감에 따른 변동성 언급.</t>
+          <t>미국 마이크론 반도체 장비 평가 완료 및 ASML 공급망 진입 뉴스. 시가총액 3조 벨류 및 10만 멜콘 목표.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['로봇', '품절주', '인수']</t>
+          <t>['반도체 장비', 'ASML', '마이크론']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>030530</t>
+          <t>179880</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>샌즈랩</t>
+          <t>원익홀딩스</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9700</v>
+        <v>28050</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+18.29%</t>
+          <t>'+18.11%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.27</v>
+        <v>-0.15</v>
       </c>
       <c r="E4" t="n">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="F4" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="G4" t="n">
-        <v>72</v>
+        <v>183</v>
       </c>
       <c r="H4" t="n">
-        <v>1.42</v>
+        <v>5.16</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,38 +779,38 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>8200</v>
+        <v>23750</v>
       </c>
       <c r="K4" t="n">
-        <v>8230</v>
+        <v>24200</v>
       </c>
       <c r="L4" t="n">
-        <v>9780</v>
+        <v>29900</v>
       </c>
       <c r="M4" t="n">
-        <v>8100</v>
+        <v>24200</v>
       </c>
       <c r="N4" t="n">
-        <v>1.15</v>
+        <v>5.31</v>
       </c>
       <c r="O4" t="n">
-        <v>96174223590</v>
+        <v>150714115450</v>
       </c>
       <c r="P4" t="n">
-        <v>9820</v>
+        <v>50600</v>
       </c>
       <c r="Q4" t="n">
-        <v>2965</v>
+        <v>13210</v>
       </c>
       <c r="R4" t="n">
-        <v>-63000</v>
+        <v>-35000</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>126000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>샌즈랩, 미국 양자컴퓨터 및 보안주 강세와 국내 IT 보안 사고 뉴스에 따른 관심 증가. AI 시대 보안 중요성 부각.</t>
+          <t>원익홀딩스, 로봇 관련주로 주목받으며 기대감 형성. 다만, 구체적인 호재보다는 기대감에 따른 변동성 언급.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['AI 보안', '양자컴퓨터', 'IT 보안']</t>
+          <t>['로봇', '품절주', '인수']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -832,38 +832,38 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>411080</t>
+          <t>030530</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>멜콘</t>
+          <t>샌즈랩</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>17900</v>
+        <v>9320</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+13.08%</t>
+          <t>'+13.66%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1.02</v>
+        <v>0.27</v>
       </c>
       <c r="E5" t="n">
-        <v>126</v>
+        <v>74</v>
       </c>
       <c r="F5" t="n">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="G5" t="n">
-        <v>238</v>
+        <v>72</v>
       </c>
       <c r="H5" t="n">
-        <v>1.11</v>
+        <v>1.42</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,314 +871,314 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>15830</v>
+        <v>8200</v>
       </c>
       <c r="K5" t="n">
-        <v>17170</v>
+        <v>8230</v>
       </c>
       <c r="L5" t="n">
-        <v>18530</v>
+        <v>9780</v>
       </c>
       <c r="M5" t="n">
-        <v>15830</v>
+        <v>8100</v>
       </c>
       <c r="N5" t="n">
-        <v>0.09</v>
+        <v>1.15</v>
       </c>
       <c r="O5" t="n">
-        <v>211806854965</v>
+        <v>102516476060</v>
       </c>
       <c r="P5" t="n">
-        <v>28800</v>
+        <v>9820</v>
       </c>
       <c r="Q5" t="n">
-        <v>11550</v>
+        <v>2965</v>
       </c>
       <c r="R5" t="n">
-        <v>-21000</v>
+        <v>-63000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>미국 마이크론 반도체 장비 평가 완료 및 ASML 공급망 진입 뉴스 기반 긍정적 전망. 적정 밸류에이션 언급.</t>
+          <t>샌즈랩, 미국 양자컴퓨터 및 보안주 강세와 국내 IT 보안 사고 뉴스에 따른 관심 증가. AI 시대 보안 중요성 부각.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['반도체 장비', '마이크론', '공급망']</t>
+          <t>['AI 보안', '양자컴퓨터', 'IT 보안']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>179880</t>
+          <t>411080</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>나무가</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>187100</v>
+        <v>18810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+9.35%</t>
+          <t>'+10.06%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.01</v>
+        <v>0.61</v>
       </c>
       <c r="E6" t="n">
-        <v>65</v>
+        <v>116</v>
       </c>
       <c r="F6" t="n">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="G6" t="n">
-        <v>263</v>
+        <v>311</v>
       </c>
       <c r="H6" t="n">
-        <v>74.90000000000001</v>
+        <v>4.74</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>171100</v>
+        <v>17090</v>
       </c>
       <c r="K6" t="n">
-        <v>176300</v>
+        <v>19270</v>
       </c>
       <c r="L6" t="n">
-        <v>189000</v>
+        <v>20450</v>
       </c>
       <c r="M6" t="n">
-        <v>175400</v>
+        <v>18070</v>
       </c>
       <c r="N6" t="n">
-        <v>74.89</v>
+        <v>4.13</v>
       </c>
       <c r="O6" t="n">
-        <v>525265350600</v>
+        <v>41811582250</v>
       </c>
       <c r="P6" t="n">
-        <v>243500</v>
+        <v>28600</v>
       </c>
       <c r="Q6" t="n">
-        <v>71000</v>
+        <v>11050</v>
       </c>
       <c r="R6" t="n">
-        <v>654000</v>
+        <v>-34000</v>
       </c>
       <c r="S6" t="n">
-        <v>-1000</v>
+        <v>9000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>삼성전자우, 외국인 매수세 및 숏 스퀴즈 가능성 언급. 자사주 매입 기대.</t>
+          <t>아틀라스 발주 및 AI 데이터센터 방열시스템 공급 계약. 로봇주 중 최고 실적 및 가격 경쟁력.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['숏 스퀴즈', '자사주매입', '우선주']</t>
+          <t>['아틀라스', '휴머노이드', '로봇주']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>190510</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>나무가</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>18630</v>
+        <v>188100</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+9.01%</t>
+          <t>'+9.94%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.61</v>
+        <v>0.01</v>
       </c>
       <c r="E7" t="n">
-        <v>114</v>
+        <v>65</v>
       </c>
       <c r="F7" t="n">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="G7" t="n">
-        <v>307</v>
+        <v>271</v>
       </c>
       <c r="H7" t="n">
-        <v>4.74</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>17090</v>
+        <v>171100</v>
       </c>
       <c r="K7" t="n">
-        <v>19270</v>
+        <v>176300</v>
       </c>
       <c r="L7" t="n">
-        <v>20450</v>
+        <v>189000</v>
       </c>
       <c r="M7" t="n">
-        <v>18070</v>
+        <v>175400</v>
       </c>
       <c r="N7" t="n">
-        <v>4.13</v>
+        <v>74.89</v>
       </c>
       <c r="O7" t="n">
-        <v>40468113620</v>
+        <v>533405873450</v>
       </c>
       <c r="P7" t="n">
-        <v>28600</v>
+        <v>243500</v>
       </c>
       <c r="Q7" t="n">
-        <v>11050</v>
+        <v>71000</v>
       </c>
       <c r="R7" t="n">
-        <v>-34000</v>
+        <v>654000</v>
       </c>
       <c r="S7" t="n">
-        <v>9000</v>
+        <v>-1000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>아틀라스 발주 및 휴머노이드 로봇 관련 호재로 인한 상승 기대. 카메라 모듈 및 로봇 부품 대장 언급.</t>
+          <t>삼성전자우, 외국인 매수세 및 숏 스퀴즈 가능성 언급. 자사주 매입 기대.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['로봇주', '아틀라스', '카메라모듈']</t>
+          <t>['숏 스퀴즈', '자사주매입', '우선주']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>190510</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14900</v>
+        <v>1462000</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+8.76%</t>
+          <t>'+9.02%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.05</v>
+        <v>-0.05</v>
       </c>
       <c r="E8" t="n">
-        <v>125</v>
+        <v>800</v>
       </c>
       <c r="F8" t="n">
-        <v>63</v>
+        <v>513</v>
       </c>
       <c r="G8" t="n">
-        <v>460</v>
+        <v>1781</v>
       </c>
       <c r="H8" t="n">
-        <v>2.87</v>
+        <v>48.61</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>13700</v>
+        <v>1341000</v>
       </c>
       <c r="K8" t="n">
-        <v>14210</v>
+        <v>1390000</v>
       </c>
       <c r="L8" t="n">
-        <v>15290</v>
+        <v>1467000</v>
       </c>
       <c r="M8" t="n">
-        <v>14210</v>
+        <v>1358000</v>
       </c>
       <c r="N8" t="n">
-        <v>2.82</v>
+        <v>48.66</v>
       </c>
       <c r="O8" t="n">
-        <v>147728730850</v>
+        <v>3348733879000</v>
       </c>
       <c r="P8" t="n">
-        <v>31500</v>
+        <v>2987000</v>
       </c>
       <c r="Q8" t="n">
-        <v>1760</v>
+        <v>501000</v>
       </c>
       <c r="R8" t="n">
-        <v>247000</v>
+        <v>53000</v>
       </c>
       <c r="S8" t="n">
-        <v>3000</v>
+        <v>55000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>메타 유리기판 및 해상광통신 케이블 관련 뉴스 기반 상승 기대. 외인 프로그램 적극 매수.</t>
+          <t>29년 완판 및 자사주 20조 취득 발표. 반도체 업황 불신 해소 및 주가 상승 전망.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,11 +1187,11 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['해상광통신', '유리기판', '외국인매수']</t>
+          <t>['HBM', '자사주 매입', '실적']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,90 +1200,90 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1452000</v>
+        <v>14910</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+8.28%</t>
+          <t>'+8.83%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.05</v>
+        <v>0.05</v>
       </c>
       <c r="E9" t="n">
-        <v>800</v>
+        <v>127</v>
       </c>
       <c r="F9" t="n">
-        <v>511</v>
+        <v>63</v>
       </c>
       <c r="G9" t="n">
-        <v>1812</v>
+        <v>472</v>
       </c>
       <c r="H9" t="n">
-        <v>48.61</v>
+        <v>2.87</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>1341000</v>
+        <v>13700</v>
       </c>
       <c r="K9" t="n">
-        <v>1390000</v>
+        <v>14210</v>
       </c>
       <c r="L9" t="n">
-        <v>1467000</v>
+        <v>15290</v>
       </c>
       <c r="M9" t="n">
-        <v>1358000</v>
+        <v>14210</v>
       </c>
       <c r="N9" t="n">
-        <v>48.66</v>
+        <v>2.82</v>
       </c>
       <c r="O9" t="n">
-        <v>3291510345000</v>
+        <v>149707365830</v>
       </c>
       <c r="P9" t="n">
-        <v>2987000</v>
+        <v>31500</v>
       </c>
       <c r="Q9" t="n">
-        <v>501000</v>
+        <v>1760</v>
       </c>
       <c r="R9" t="n">
-        <v>53000</v>
+        <v>247000</v>
       </c>
       <c r="S9" t="n">
-        <v>55000</v>
+        <v>3000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2029년 완판 및 자사주 20조 취득 발표 기반 긍정적 전망. 반도체 업황 회복 기대.</t>
+          <t>메타 유리기판 및 해상광통신 케이블 관련 뉴스 기반 상승 기대. 외인 프로그램 적극 매수.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['반도체 업황', '자사주 매입', '컨퍼런스콜']</t>
+          <t>['해상광통신', '유리기판', '외국인매수']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>239500</v>
+        <v>240500</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+7.88%</t>
+          <t>'+8.33%</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1317,10 +1317,10 @@
         <v>800</v>
       </c>
       <c r="F10" t="n">
-        <v>486</v>
+        <v>492</v>
       </c>
       <c r="G10" t="n">
-        <v>1718</v>
+        <v>1686</v>
       </c>
       <c r="H10" t="n">
         <v>46.15</v>
@@ -1346,7 +1346,7 @@
         <v>46.1</v>
       </c>
       <c r="O10" t="n">
-        <v>2231587594000</v>
+        <v>2269688106250</v>
       </c>
       <c r="P10" t="n">
         <v>374500</v>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>HBM4 점유율 경쟁 및 피봇 후 반등 기대감. 일부 감정적 발언 포함.</t>
+          <t>HBM4 점유율 경쟁 및 하반기 상승 기대. 하지만 정치적 언급 다수 포함.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['HBM4', '점유율', '반등']</t>
+          <t>['HBM4', '점유율', '경쟁']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2595</v>
+        <v>2565</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+5.92%</t>
+          <t>'+4.69%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.68</v>
       </c>
       <c r="E11" t="n">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="F11" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="G11" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H11" t="n">
         <v>1.69</v>
@@ -1438,7 +1438,7 @@
         <v>1.01</v>
       </c>
       <c r="O11" t="n">
-        <v>71011787689</v>
+        <v>72573370997</v>
       </c>
       <c r="P11" t="n">
         <v>2965</v>
@@ -1454,16 +1454,16 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>개인 물량 흡수 및 계단식 하락 후 반등 기대감이 있으나, 음봉 마감 및 전환사채 전환 관련 불확실성도 존재합니다.</t>
+          <t>거래량 증가 및 개인 물량 흡수 관찰. 시세 분출 기간 진입 기대감.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['개인 물량', '계단식 하락', '전환사채']</t>
+          <t>['거래량', '개인물량', '시세분출']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>182000</v>
+        <v>181900</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+4.42%</t>
+          <t>'+4.36%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>-0.06</v>
       </c>
       <c r="E12" t="n">
-        <v>513</v>
+        <v>527</v>
       </c>
       <c r="F12" t="n">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="G12" t="n">
-        <v>1585</v>
+        <v>1658</v>
       </c>
       <c r="H12" t="n">
         <v>35.43</v>
@@ -1530,7 +1530,7 @@
         <v>35.49</v>
       </c>
       <c r="O12" t="n">
-        <v>111854483100</v>
+        <v>113686149850</v>
       </c>
       <c r="P12" t="n">
         <v>304000</v>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>코스피 지수 대비 낮은 상승률 및 공매도 비율에 대한 부정적 의견. 신한증권 매도세 지적.</t>
+          <t>상승장 속 소외 및 공매도 비율에 대한 불만. 프로그램 매수세 관찰.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['공매도', '지수대비', '신한증권']</t>
+          <t>['공매도', '프로그램매수', '소외']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>64000</v>
+        <v>63900</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+2.89%</t>
+          <t>'+2.73%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>0.57</v>
       </c>
       <c r="E13" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F13" t="n">
         <v>63</v>
       </c>
       <c r="G13" t="n">
-        <v>504</v>
+        <v>510</v>
       </c>
       <c r="H13" t="n">
         <v>41.01</v>
@@ -1622,7 +1622,7 @@
         <v>40.44</v>
       </c>
       <c r="O13" t="n">
-        <v>161078320450</v>
+        <v>163118328750</v>
       </c>
       <c r="P13" t="n">
         <v>67300</v>
@@ -1682,13 +1682,13 @@
         <v>-0.01</v>
       </c>
       <c r="E14" t="n">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="F14" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G14" t="n">
-        <v>353</v>
+        <v>364</v>
       </c>
       <c r="H14" t="n">
         <v>28.81</v>
@@ -1714,7 +1714,7 @@
         <v>28.82</v>
       </c>
       <c r="O14" t="n">
-        <v>24798541675</v>
+        <v>25298126975</v>
       </c>
       <c r="P14" t="n">
         <v>69700</v>
@@ -1759,184 +1759,184 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>앤로보틱스</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>16390</v>
+        <v>2200</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+0.00%</t>
+          <t>'+1.38%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.18</v>
       </c>
       <c r="E15" t="n">
-        <v>97</v>
+        <v>67</v>
       </c>
       <c r="F15" t="n">
-        <v>69</v>
+        <v>40</v>
       </c>
       <c r="G15" t="n">
-        <v>247</v>
+        <v>228</v>
       </c>
       <c r="H15" t="n">
-        <v>28.03</v>
+        <v>5.07</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>16390</v>
+        <v>2170</v>
       </c>
       <c r="K15" t="n">
-        <v>16630</v>
+        <v>2160</v>
       </c>
       <c r="L15" t="n">
-        <v>16760</v>
+        <v>2475</v>
       </c>
       <c r="M15" t="n">
-        <v>16300</v>
+        <v>2155</v>
       </c>
       <c r="N15" t="n">
-        <v>27.96</v>
+        <v>4.89</v>
       </c>
       <c r="O15" t="n">
-        <v>33536926705</v>
+        <v>44436253815</v>
       </c>
       <c r="P15" t="n">
-        <v>35350</v>
+        <v>4980</v>
       </c>
       <c r="Q15" t="n">
-        <v>16270</v>
+        <v>774</v>
       </c>
       <c r="R15" t="n">
-        <v>-375000</v>
+        <v>439000</v>
       </c>
       <c r="S15" t="n">
-        <v>-35000</v>
+        <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>수주 물량 대비 주가 부진 지속. 애널리스트 목표주가 하향 및 공매도 의혹 제기.</t>
+          <t>로봇 섹터 강세 속 앤로보틱스 주가 움직임에 대한 기대와 우려가 공존. 자사주 매도 및 신용 증가 등 혼조세.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['수주', '주가 부진', '공매도']</t>
+          <t>['로봇 섹터', '신용 증가', '자사주 매도']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>138360</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>앤로보틱스</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2165</v>
+        <v>16390</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-0.23%</t>
+          <t>'+0.00%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.18</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>63</v>
+        <v>99</v>
       </c>
       <c r="F16" t="n">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="G16" t="n">
-        <v>225</v>
+        <v>258</v>
       </c>
       <c r="H16" t="n">
-        <v>5.07</v>
+        <v>28.03</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>2170</v>
+        <v>16390</v>
       </c>
       <c r="K16" t="n">
-        <v>2160</v>
+        <v>16630</v>
       </c>
       <c r="L16" t="n">
-        <v>2475</v>
+        <v>16760</v>
       </c>
       <c r="M16" t="n">
-        <v>2155</v>
+        <v>16300</v>
       </c>
       <c r="N16" t="n">
-        <v>4.89</v>
+        <v>27.96</v>
       </c>
       <c r="O16" t="n">
-        <v>44063878368</v>
+        <v>34124190850</v>
       </c>
       <c r="P16" t="n">
-        <v>4980</v>
+        <v>35350</v>
       </c>
       <c r="Q16" t="n">
-        <v>774</v>
+        <v>16270</v>
       </c>
       <c r="R16" t="n">
-        <v>439000</v>
+        <v>-375000</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>-35000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>로봇 섹터 강세 속 앤로보틱스 주가 움직임에 대한 기대와 우려가 공존. 자사주 매도 및 신용 증가 등 혼조세.</t>
+          <t>수주 전망은 긍정적이나, 증권사 목표주가 및 조선업 전반에 대한 불신 존재.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['로봇 섹터', '신용 증가', '자사주 매도']</t>
+          <t>['수주', '목표주가', '조선업']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>138360</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
@@ -1958,13 +1958,13 @@
         <v>-0.03</v>
       </c>
       <c r="E17" t="n">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="F17" t="n">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="G17" t="n">
-        <v>994</v>
+        <v>1012</v>
       </c>
       <c r="H17" t="n">
         <v>10.31</v>
@@ -1990,7 +1990,7 @@
         <v>10.34</v>
       </c>
       <c r="O17" t="n">
-        <v>56696043300</v>
+        <v>56900858950</v>
       </c>
       <c r="P17" t="n">
         <v>154800</v>
@@ -2006,16 +2006,16 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>실적 발표 대비 주가 하락 및 부정적 전망. 대주주 매도와 외국인 매도세 언급.</t>
+          <t>미 해군 상륙함 건조 제안 및 한미 정상회담 관련 호재 뉴스. 그러나 주가 하락 및 투자 회의론.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['실적', '주가하락', '외국인매도']</t>
+          <t>['상륙함', '건조', '정상회담']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>14110</v>
+        <v>14135</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-2.35%</t>
+          <t>'-2.18%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>-0.19</v>
       </c>
       <c r="E18" t="n">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="F18" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="G18" t="n">
-        <v>366</v>
+        <v>385</v>
       </c>
       <c r="H18" t="n">
         <v>9.83</v>
@@ -2082,7 +2082,7 @@
         <v>10.02</v>
       </c>
       <c r="O18" t="n">
-        <v>46332765735</v>
+        <v>47179371285</v>
       </c>
       <c r="P18" t="n">
         <v>40350</v>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>주가 하락 및 경영진에 대한 불신, 사기꾼 언급 등 부정적 심리. 객관적 근거 부족.</t>
+          <t>심각한 주가 하락과 경영진 비판. 회사의 실질적인 사업 내용에 대한 언급 부족.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['주가조작', '개잡주', '경영진']</t>
+          <t>['주가조작', '경영진', '비판']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2131,11 +2131,11 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2010</v>
+        <v>2020</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-3.60%</t>
+          <t>'-3.12%</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -2174,7 +2174,7 @@
         <v>2.13</v>
       </c>
       <c r="O19" t="n">
-        <v>13798073822</v>
+        <v>13882156184</v>
       </c>
       <c r="P19" t="n">
         <v>6190</v>

--- a/data/trending_integrated_20261028_12.xlsx
+++ b/data/trending_integrated_20261028_12.xlsx
@@ -578,13 +578,13 @@
         <v>-0.19</v>
       </c>
       <c r="E2" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F2" t="n">
         <v>75</v>
       </c>
       <c r="G2" t="n">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="H2" t="n">
         <v>1.2</v>
@@ -610,7 +610,7 @@
         <v>1.39</v>
       </c>
       <c r="O2" t="n">
-        <v>149729535316</v>
+        <v>149874338326</v>
       </c>
       <c r="P2" t="n">
         <v>8100</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18950</v>
+        <v>19170</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+19.71%</t>
+          <t>'+21.10%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>1.02</v>
       </c>
       <c r="E3" t="n">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="F3" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="G3" t="n">
-        <v>263</v>
+        <v>276</v>
       </c>
       <c r="H3" t="n">
         <v>1.11</v>
@@ -693,7 +693,7 @@
         <v>17170</v>
       </c>
       <c r="L3" t="n">
-        <v>19055</v>
+        <v>19190</v>
       </c>
       <c r="M3" t="n">
         <v>15830</v>
@@ -702,7 +702,7 @@
         <v>0.09</v>
       </c>
       <c r="O3" t="n">
-        <v>236304437150</v>
+        <v>253293082880</v>
       </c>
       <c r="P3" t="n">
         <v>28800</v>
@@ -718,7 +718,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>미국 마이크론 반도체 장비 평가 완료 및 ASML 공급망 진입 뉴스. 시가총액 3조 벨류 및 10만 멜콘 목표.</t>
+          <t>미국 마이크론 반도체 장비 평가 완료 및 ASML 공급망 진입 뉴스. 시가총액 3조 목표 및 10만 멜콘 가자.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['반도체 장비', 'ASML', '마이크론']</t>
+          <t>['반도체 장비', '공급망', '시가총액']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>28050</v>
+        <v>27800</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+18.11%</t>
+          <t>'+17.05%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.15</v>
       </c>
       <c r="E4" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F4" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G4" t="n">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="H4" t="n">
         <v>5.16</v>
@@ -794,7 +794,7 @@
         <v>5.31</v>
       </c>
       <c r="O4" t="n">
-        <v>150714115450</v>
+        <v>155202517675</v>
       </c>
       <c r="P4" t="n">
         <v>50600</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9320</v>
+        <v>9240</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+13.66%</t>
+          <t>'+12.68%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.27</v>
       </c>
       <c r="E5" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F5" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G5" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H5" t="n">
         <v>1.42</v>
@@ -886,7 +886,7 @@
         <v>1.15</v>
       </c>
       <c r="O5" t="n">
-        <v>102516476060</v>
+        <v>106348656540</v>
       </c>
       <c r="P5" t="n">
         <v>9820</v>
@@ -931,123 +931,123 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>나무가</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18810</v>
+        <v>188300</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+10.06%</t>
+          <t>'+10.05%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.61</v>
+        <v>0.01</v>
       </c>
       <c r="E6" t="n">
-        <v>116</v>
+        <v>67</v>
       </c>
       <c r="F6" t="n">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="G6" t="n">
-        <v>311</v>
+        <v>277</v>
       </c>
       <c r="H6" t="n">
-        <v>4.74</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>17090</v>
+        <v>171100</v>
       </c>
       <c r="K6" t="n">
-        <v>19270</v>
+        <v>176300</v>
       </c>
       <c r="L6" t="n">
-        <v>20450</v>
+        <v>189000</v>
       </c>
       <c r="M6" t="n">
-        <v>18070</v>
+        <v>175400</v>
       </c>
       <c r="N6" t="n">
-        <v>4.13</v>
+        <v>74.89</v>
       </c>
       <c r="O6" t="n">
-        <v>41811582250</v>
+        <v>540912995250</v>
       </c>
       <c r="P6" t="n">
-        <v>28600</v>
+        <v>243500</v>
       </c>
       <c r="Q6" t="n">
-        <v>11050</v>
+        <v>71000</v>
       </c>
       <c r="R6" t="n">
-        <v>-34000</v>
+        <v>654000</v>
       </c>
       <c r="S6" t="n">
-        <v>9000</v>
+        <v>-1000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>아틀라스 발주 및 AI 데이터센터 방열시스템 공급 계약. 로봇주 중 최고 실적 및 가격 경쟁력.</t>
+          <t>삼성전자우, 외국인 매수세 및 숏 스퀴즈 가능성 언급. 자사주 매입 기대.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['아틀라스', '휴머노이드', '로봇주']</t>
+          <t>['숏 스퀴즈', '자사주매입', '우선주']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>190510</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>188100</v>
+        <v>1468000</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+9.94%</t>
+          <t>'+9.47%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.01</v>
+        <v>-0.05</v>
       </c>
       <c r="E7" t="n">
-        <v>65</v>
+        <v>800</v>
       </c>
       <c r="F7" t="n">
-        <v>50</v>
+        <v>526</v>
       </c>
       <c r="G7" t="n">
-        <v>271</v>
+        <v>1838</v>
       </c>
       <c r="H7" t="n">
-        <v>74.90000000000001</v>
+        <v>48.61</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,130 +1055,130 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>171100</v>
+        <v>1341000</v>
       </c>
       <c r="K7" t="n">
-        <v>176300</v>
+        <v>1390000</v>
       </c>
       <c r="L7" t="n">
-        <v>189000</v>
+        <v>1470000</v>
       </c>
       <c r="M7" t="n">
-        <v>175400</v>
+        <v>1358000</v>
       </c>
       <c r="N7" t="n">
-        <v>74.89</v>
+        <v>48.66</v>
       </c>
       <c r="O7" t="n">
-        <v>533405873450</v>
+        <v>3457796178000</v>
       </c>
       <c r="P7" t="n">
-        <v>243500</v>
+        <v>2987000</v>
       </c>
       <c r="Q7" t="n">
-        <v>71000</v>
+        <v>501000</v>
       </c>
       <c r="R7" t="n">
-        <v>654000</v>
+        <v>53000</v>
       </c>
       <c r="S7" t="n">
-        <v>-1000</v>
+        <v>55000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>삼성전자우, 외국인 매수세 및 숏 스퀴즈 가능성 언급. 자사주 매입 기대.</t>
+          <t>2029년 완판 전망으로 글로벌 반도체 업황 불신 해소. 자사주 20조 취득 및 200만원 목표가 제시.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['숏 스퀴즈', '자사주매입', '우선주']</t>
+          <t>['반도체 업황', '자사주 매입', '목표가']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1462000</v>
+        <v>14990</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+9.02%</t>
+          <t>'+9.42%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.05</v>
+        <v>0.05</v>
       </c>
       <c r="E8" t="n">
-        <v>800</v>
+        <v>132</v>
       </c>
       <c r="F8" t="n">
-        <v>513</v>
+        <v>66</v>
       </c>
       <c r="G8" t="n">
-        <v>1781</v>
+        <v>505</v>
       </c>
       <c r="H8" t="n">
-        <v>48.61</v>
+        <v>2.87</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>1341000</v>
+        <v>13700</v>
       </c>
       <c r="K8" t="n">
-        <v>1390000</v>
+        <v>14210</v>
       </c>
       <c r="L8" t="n">
-        <v>1467000</v>
+        <v>15290</v>
       </c>
       <c r="M8" t="n">
-        <v>1358000</v>
+        <v>14210</v>
       </c>
       <c r="N8" t="n">
-        <v>48.66</v>
+        <v>2.82</v>
       </c>
       <c r="O8" t="n">
-        <v>3348733879000</v>
+        <v>151747193460</v>
       </c>
       <c r="P8" t="n">
-        <v>2987000</v>
+        <v>31500</v>
       </c>
       <c r="Q8" t="n">
-        <v>501000</v>
+        <v>1760</v>
       </c>
       <c r="R8" t="n">
-        <v>53000</v>
+        <v>247000</v>
       </c>
       <c r="S8" t="n">
-        <v>55000</v>
+        <v>3000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>29년 완판 및 자사주 20조 취득 발표. 반도체 업황 불신 해소 및 주가 상승 전망.</t>
+          <t>메타 유리기판 및 해상광통신 케이블 관련 기대감. 외인 프로그램 적극 매수 및 공매도 압박.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,11 +1187,11 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['HBM', '자사주 매입', '실적']</t>
+          <t>['유리기판', '해상광통신', '외인 매수']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,90 +1200,90 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14910</v>
+        <v>240750</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+8.83%</t>
+          <t>'+8.45%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>0.05</v>
       </c>
       <c r="E9" t="n">
-        <v>127</v>
+        <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>63</v>
+        <v>492</v>
       </c>
       <c r="G9" t="n">
-        <v>472</v>
+        <v>1701</v>
       </c>
       <c r="H9" t="n">
-        <v>2.87</v>
+        <v>46.15</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>13700</v>
+        <v>222000</v>
       </c>
       <c r="K9" t="n">
-        <v>14210</v>
+        <v>231000</v>
       </c>
       <c r="L9" t="n">
-        <v>15290</v>
+        <v>243000</v>
       </c>
       <c r="M9" t="n">
-        <v>14210</v>
+        <v>228000</v>
       </c>
       <c r="N9" t="n">
-        <v>2.82</v>
+        <v>46.1</v>
       </c>
       <c r="O9" t="n">
-        <v>149707365830</v>
+        <v>2327632200250</v>
       </c>
       <c r="P9" t="n">
-        <v>31500</v>
+        <v>374500</v>
       </c>
       <c r="Q9" t="n">
-        <v>1760</v>
+        <v>94500</v>
       </c>
       <c r="R9" t="n">
-        <v>247000</v>
+        <v>1304000</v>
       </c>
       <c r="S9" t="n">
-        <v>3000</v>
+        <v>524000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>메타 유리기판 및 해상광통신 케이블 관련 뉴스 기반 상승 기대. 외인 프로그램 적극 매수.</t>
+          <t>노무라 증권의 목표가 상향 및 HBM4 점유율 경쟁 기대감. 긍정적인 시장 분위기 속 상승 전망.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['해상광통신', '유리기판', '외국인매수']</t>
+          <t>['HBM4', '노무라 증권', '반등']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,90 +1292,90 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>나무가</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>240500</v>
+        <v>18330</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+8.33%</t>
+          <t>'+7.26%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.05</v>
+        <v>0.61</v>
       </c>
       <c r="E10" t="n">
-        <v>800</v>
+        <v>118</v>
       </c>
       <c r="F10" t="n">
-        <v>492</v>
+        <v>63</v>
       </c>
       <c r="G10" t="n">
-        <v>1686</v>
+        <v>313</v>
       </c>
       <c r="H10" t="n">
-        <v>46.15</v>
+        <v>4.74</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>222000</v>
+        <v>17090</v>
       </c>
       <c r="K10" t="n">
-        <v>231000</v>
+        <v>19270</v>
       </c>
       <c r="L10" t="n">
-        <v>243000</v>
+        <v>20450</v>
       </c>
       <c r="M10" t="n">
-        <v>228000</v>
+        <v>18070</v>
       </c>
       <c r="N10" t="n">
-        <v>46.1</v>
+        <v>4.13</v>
       </c>
       <c r="O10" t="n">
-        <v>2269688106250</v>
+        <v>42852924970</v>
       </c>
       <c r="P10" t="n">
-        <v>374500</v>
+        <v>28600</v>
       </c>
       <c r="Q10" t="n">
-        <v>94500</v>
+        <v>11050</v>
       </c>
       <c r="R10" t="n">
-        <v>1304000</v>
+        <v>-34000</v>
       </c>
       <c r="S10" t="n">
-        <v>524000</v>
+        <v>9000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>HBM4 점유율 경쟁 및 하반기 상승 기대. 하지만 정치적 언급 다수 포함.</t>
+          <t>아틀라스 1만대 발주 및 AI 데이터센터 방열시스템 공급 계약 체결. 삼성+아틀라스 공급망 및 로봇주 중 최고 실적.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['HBM4', '점유율', '경쟁']</t>
+          <t>['아틀라스', 'AI 데이터센터', '로봇주']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>190510</t>
         </is>
       </c>
     </row>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2565</v>
+        <v>2590</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+4.69%</t>
+          <t>'+5.71%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.68</v>
       </c>
       <c r="E11" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F11" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G11" t="n">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="H11" t="n">
         <v>1.69</v>
@@ -1438,7 +1438,7 @@
         <v>1.01</v>
       </c>
       <c r="O11" t="n">
-        <v>72573370997</v>
+        <v>73353332936</v>
       </c>
       <c r="P11" t="n">
         <v>2965</v>
@@ -1454,16 +1454,16 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>거래량 증가 및 개인 물량 흡수 관찰. 시세 분출 기간 진입 기대감.</t>
+          <t>거래량 증가 및 개인 물량 흡수 중. 3000원 돌파 기대감 및 외인 매수세 유입.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['거래량', '개인물량', '시세분출']</t>
+          <t>['거래량', '외국인', '시세 분출']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1498,13 +1498,13 @@
         <v>-0.06</v>
       </c>
       <c r="E12" t="n">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="F12" t="n">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="G12" t="n">
-        <v>1658</v>
+        <v>1766</v>
       </c>
       <c r="H12" t="n">
         <v>35.43</v>
@@ -1530,7 +1530,7 @@
         <v>35.49</v>
       </c>
       <c r="O12" t="n">
-        <v>113686149850</v>
+        <v>115571690950</v>
       </c>
       <c r="P12" t="n">
         <v>304000</v>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>상승장 속 소외 및 공매도 비율에 대한 불만. 프로그램 매수세 관찰.</t>
+          <t>호재에도 불구하고 주가 상승 미미. 프로그램 매수 외에는 긍정적 모멘텀 부족 및 공매도 비율 부담.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['공매도', '프로그램매수', '소외']</t>
+          <t>['공매도', '프로그램 매수', '주가 부진']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>63900</v>
+        <v>64200</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+2.73%</t>
+          <t>'+3.22%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>0.57</v>
       </c>
       <c r="E13" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F13" t="n">
         <v>63</v>
       </c>
       <c r="G13" t="n">
-        <v>510</v>
+        <v>526</v>
       </c>
       <c r="H13" t="n">
         <v>41.01</v>
@@ -1622,7 +1622,7 @@
         <v>40.44</v>
       </c>
       <c r="O13" t="n">
-        <v>163118328750</v>
+        <v>166539903000</v>
       </c>
       <c r="P13" t="n">
         <v>67300</v>
@@ -1682,13 +1682,13 @@
         <v>-0.01</v>
       </c>
       <c r="E14" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="F14" t="n">
         <v>70</v>
       </c>
       <c r="G14" t="n">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="H14" t="n">
         <v>28.81</v>
@@ -1714,7 +1714,7 @@
         <v>28.82</v>
       </c>
       <c r="O14" t="n">
-        <v>25298126975</v>
+        <v>25869097650</v>
       </c>
       <c r="P14" t="n">
         <v>69700</v>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2200</v>
+        <v>2210</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+1.38%</t>
+          <t>'+1.84%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>0.18</v>
       </c>
       <c r="E15" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="F15" t="n">
         <v>40</v>
       </c>
       <c r="G15" t="n">
-        <v>228</v>
+        <v>246</v>
       </c>
       <c r="H15" t="n">
         <v>5.07</v>
@@ -1806,7 +1806,7 @@
         <v>4.89</v>
       </c>
       <c r="O15" t="n">
-        <v>44436253815</v>
+        <v>44827355373</v>
       </c>
       <c r="P15" t="n">
         <v>4980</v>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>16390</v>
+        <v>16380</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'+0.00%</t>
+          <t>'-0.06%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="F16" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G16" t="n">
-        <v>258</v>
+        <v>281</v>
       </c>
       <c r="H16" t="n">
         <v>28.03</v>
@@ -1898,7 +1898,7 @@
         <v>27.96</v>
       </c>
       <c r="O16" t="n">
-        <v>34124190850</v>
+        <v>34979466750</v>
       </c>
       <c r="P16" t="n">
         <v>35350</v>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>수주 전망은 긍정적이나, 증권사 목표주가 및 조선업 전반에 대한 불신 존재.</t>
+          <t>주문량 대비 주가 부진 및 증권사 목표가 하향에 대한 불만. 실적 발표에도 주가 흐름 미미.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['수주', '목표주가', '조선업']</t>
+          <t>['실적', '목표주가', '조선주']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1958,13 +1958,13 @@
         <v>-0.03</v>
       </c>
       <c r="E17" t="n">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="F17" t="n">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="G17" t="n">
-        <v>1012</v>
+        <v>1031</v>
       </c>
       <c r="H17" t="n">
         <v>10.31</v>
@@ -1990,7 +1990,7 @@
         <v>10.34</v>
       </c>
       <c r="O17" t="n">
-        <v>56900858950</v>
+        <v>57237321200</v>
       </c>
       <c r="P17" t="n">
         <v>154800</v>
@@ -2006,16 +2006,16 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>미 해군 상륙함 건조 제안 및 한미 정상회담 관련 호재 뉴스. 그러나 주가 하락 및 투자 회의론.</t>
+          <t>코스피 지수 상승 속에서도 주가 하락 지속. 미국 조선업 협력 난항 및 부정적인 시장 전망.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['상륙함', '건조', '정상회담']</t>
+          <t>['잠수함', '조선업', '미국 해군']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>14135</v>
+        <v>14130</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-2.18%</t>
+          <t>'-2.21%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>-0.19</v>
       </c>
       <c r="E18" t="n">
-        <v>193</v>
+        <v>208</v>
       </c>
       <c r="F18" t="n">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="G18" t="n">
-        <v>385</v>
+        <v>428</v>
       </c>
       <c r="H18" t="n">
         <v>9.83</v>
@@ -2082,7 +2082,7 @@
         <v>10.02</v>
       </c>
       <c r="O18" t="n">
-        <v>47179371285</v>
+        <v>48371926135</v>
       </c>
       <c r="P18" t="n">
         <v>40350</v>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>심각한 주가 하락과 경영진 비판. 회사의 실질적인 사업 내용에 대한 언급 부족.</t>
+          <t>코스피 지수 상승에도 불구하고 주가 하락 및 투자자 불만 고조. 경영진의 적극적인 대응 부재에 대한 비판.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['주가조작', '경영진', '비판']</t>
+          <t>['주가 조작', '경영진', '상폐']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2131,11 +2131,11 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2020</v>
+        <v>2000</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-3.12%</t>
+          <t>'-4.08%</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -2148,7 +2148,7 @@
         <v>54</v>
       </c>
       <c r="G19" t="n">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="H19" t="n">
         <v>2.52</v>
@@ -2174,7 +2174,7 @@
         <v>2.13</v>
       </c>
       <c r="O19" t="n">
-        <v>13882156184</v>
+        <v>14108009034</v>
       </c>
       <c r="P19" t="n">
         <v>6190</v>

--- a/data/trending_integrated_20261028_12.xlsx
+++ b/data/trending_integrated_20261028_12.xlsx
@@ -584,7 +584,7 @@
         <v>75</v>
       </c>
       <c r="G2" t="n">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="H2" t="n">
         <v>1.2</v>
@@ -610,7 +610,7 @@
         <v>1.39</v>
       </c>
       <c r="O2" t="n">
-        <v>149874338326</v>
+        <v>149982456061</v>
       </c>
       <c r="P2" t="n">
         <v>8100</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>미국 광통신주 급등에 따른 기대감. 전고점 돌파 및 상승 가능성 언급.</t>
+          <t>미국 광통신주 급등 영향 및 전고점 돌파 시도. 긍정적 차트 분석과 함께 상한가 기대감 형성. 단기 급등 가능성.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['광통신', '상승', '전고점']</t>
+          <t>['광통신', '전고점', '상한가']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19170</v>
+        <v>19110</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+21.10%</t>
+          <t>'+20.72%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>1.02</v>
       </c>
       <c r="E3" t="n">
-        <v>151</v>
+        <v>167</v>
       </c>
       <c r="F3" t="n">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="G3" t="n">
-        <v>276</v>
+        <v>297</v>
       </c>
       <c r="H3" t="n">
         <v>1.11</v>
@@ -693,7 +693,7 @@
         <v>17170</v>
       </c>
       <c r="L3" t="n">
-        <v>19190</v>
+        <v>19440</v>
       </c>
       <c r="M3" t="n">
         <v>15830</v>
@@ -702,7 +702,7 @@
         <v>0.09</v>
       </c>
       <c r="O3" t="n">
-        <v>253293082880</v>
+        <v>265432306350</v>
       </c>
       <c r="P3" t="n">
         <v>28800</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>미국 마이크론 반도체 장비 평가 완료 및 ASML 공급망 진입 뉴스. 시가총액 3조 목표 및 10만 멜콘 가자.</t>
+          <t>미 마이크론 반도체 장비 평가 완료 및 ASML 공급망 진입 가능성. 전세계 반도체 공급망 확장 수혜 기대. 강력한 호재.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['반도체 장비', '공급망', '시가총액']</t>
+          <t>['반도체장비', '공급망', '마이크론']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>27800</v>
+        <v>27850</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+17.05%</t>
+          <t>'+17.26%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.15</v>
       </c>
       <c r="E4" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F4" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G4" t="n">
-        <v>174</v>
+        <v>228</v>
       </c>
       <c r="H4" t="n">
         <v>5.16</v>
@@ -794,7 +794,7 @@
         <v>5.31</v>
       </c>
       <c r="O4" t="n">
-        <v>155202517675</v>
+        <v>157250933225</v>
       </c>
       <c r="P4" t="n">
         <v>50600</v>
@@ -843,21 +843,21 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9240</v>
+        <v>9310</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+12.68%</t>
+          <t>'+13.54%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.27</v>
       </c>
       <c r="E5" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F5" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G5" t="n">
         <v>73</v>
@@ -886,7 +886,7 @@
         <v>1.15</v>
       </c>
       <c r="O5" t="n">
-        <v>106348656540</v>
+        <v>108927444625</v>
       </c>
       <c r="P5" t="n">
         <v>9820</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>188300</v>
+        <v>189100</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+10.05%</t>
+          <t>'+10.52%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.01</v>
       </c>
       <c r="E6" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F6" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G6" t="n">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="H6" t="n">
         <v>74.90000000000001</v>
@@ -969,7 +969,7 @@
         <v>176300</v>
       </c>
       <c r="L6" t="n">
-        <v>189000</v>
+        <v>189100</v>
       </c>
       <c r="M6" t="n">
         <v>175400</v>
@@ -978,7 +978,7 @@
         <v>74.89</v>
       </c>
       <c r="O6" t="n">
-        <v>540912995250</v>
+        <v>560048310800</v>
       </c>
       <c r="P6" t="n">
         <v>243500</v>
@@ -1027,11 +1027,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1468000</v>
+        <v>1480000</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+9.47%</t>
+          <t>'+10.37%</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1041,10 +1041,10 @@
         <v>800</v>
       </c>
       <c r="F7" t="n">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="G7" t="n">
-        <v>1838</v>
+        <v>1765</v>
       </c>
       <c r="H7" t="n">
         <v>48.61</v>
@@ -1061,7 +1061,7 @@
         <v>1390000</v>
       </c>
       <c r="L7" t="n">
-        <v>1470000</v>
+        <v>1480000</v>
       </c>
       <c r="M7" t="n">
         <v>1358000</v>
@@ -1070,7 +1070,7 @@
         <v>48.66</v>
       </c>
       <c r="O7" t="n">
-        <v>3457796178000</v>
+        <v>3558667044000</v>
       </c>
       <c r="P7" t="n">
         <v>2987000</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2029년 완판 전망으로 글로벌 반도체 업황 불신 해소. 자사주 20조 취득 및 200만원 목표가 제시.</t>
+          <t>29년까지 완판 전망 및 자사주 20조 취득 발표. 반도체 업황 불신 해소 및 주가 상승 모멘텀 확보. 긍정적 전망.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['반도체 업황', '자사주 매입', '목표가']</t>
+          <t>['반도체', '업황', '자사주']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1115,83 +1115,83 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14990</v>
+        <v>242000</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+9.42%</t>
+          <t>'+9.01%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.05</v>
       </c>
       <c r="E8" t="n">
-        <v>132</v>
+        <v>800</v>
       </c>
       <c r="F8" t="n">
-        <v>66</v>
+        <v>495</v>
       </c>
       <c r="G8" t="n">
-        <v>505</v>
+        <v>1675</v>
       </c>
       <c r="H8" t="n">
-        <v>2.87</v>
+        <v>46.15</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>13700</v>
+        <v>222000</v>
       </c>
       <c r="K8" t="n">
-        <v>14210</v>
+        <v>231000</v>
       </c>
       <c r="L8" t="n">
-        <v>15290</v>
+        <v>243000</v>
       </c>
       <c r="M8" t="n">
-        <v>14210</v>
+        <v>228000</v>
       </c>
       <c r="N8" t="n">
-        <v>2.82</v>
+        <v>46.1</v>
       </c>
       <c r="O8" t="n">
-        <v>151747193460</v>
+        <v>2395791540500</v>
       </c>
       <c r="P8" t="n">
-        <v>31500</v>
+        <v>374500</v>
       </c>
       <c r="Q8" t="n">
-        <v>1760</v>
+        <v>94500</v>
       </c>
       <c r="R8" t="n">
-        <v>247000</v>
+        <v>1304000</v>
       </c>
       <c r="S8" t="n">
-        <v>3000</v>
+        <v>524000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>메타 유리기판 및 해상광통신 케이블 관련 기대감. 외인 프로그램 적극 매수 및 공매도 압박.</t>
+          <t>HBM4 점유율 경쟁 전망 및 증권사 목표가 상향 가능성 언급. 긍정적 기대감 존재하나 구체적 근거 부족.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['유리기판', '해상광통신', '외인 매수']</t>
+          <t>['HBM4', '점유율', '증권사']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,90 +1200,90 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>240750</v>
+        <v>14910</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+8.45%</t>
+          <t>'+8.83%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>0.05</v>
       </c>
       <c r="E9" t="n">
-        <v>800</v>
+        <v>132</v>
       </c>
       <c r="F9" t="n">
-        <v>492</v>
+        <v>66</v>
       </c>
       <c r="G9" t="n">
-        <v>1701</v>
+        <v>522</v>
       </c>
       <c r="H9" t="n">
-        <v>46.15</v>
+        <v>2.87</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>222000</v>
+        <v>13700</v>
       </c>
       <c r="K9" t="n">
-        <v>231000</v>
+        <v>14210</v>
       </c>
       <c r="L9" t="n">
-        <v>243000</v>
+        <v>15290</v>
       </c>
       <c r="M9" t="n">
-        <v>228000</v>
+        <v>14210</v>
       </c>
       <c r="N9" t="n">
-        <v>46.1</v>
+        <v>2.82</v>
       </c>
       <c r="O9" t="n">
-        <v>2327632200250</v>
+        <v>153637971890</v>
       </c>
       <c r="P9" t="n">
-        <v>374500</v>
+        <v>31500</v>
       </c>
       <c r="Q9" t="n">
-        <v>94500</v>
+        <v>1760</v>
       </c>
       <c r="R9" t="n">
-        <v>1304000</v>
+        <v>247000</v>
       </c>
       <c r="S9" t="n">
-        <v>524000</v>
+        <v>3000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>노무라 증권의 목표가 상향 및 HBM4 점유율 경쟁 기대감. 긍정적인 시장 분위기 속 상승 전망.</t>
+          <t>메타 유리기판 및 해상광통신 케이블 사업 기대감. 외국인 프로그램 매수세 지속 및 공매도 세력 약화 전망. 긍정적 시세 분출 예상.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['HBM4', '노무라 증권', '반등']</t>
+          <t>['광통신', '유리기판', '외국인']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,38 +1292,38 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>나무가</t>
+          <t>삼기에너지솔루션즈</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>18330</v>
+        <v>2635</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+7.26%</t>
+          <t>'+7.55%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.61</v>
+        <v>0.68</v>
       </c>
       <c r="E10" t="n">
-        <v>118</v>
+        <v>88</v>
       </c>
       <c r="F10" t="n">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="G10" t="n">
-        <v>313</v>
+        <v>100</v>
       </c>
       <c r="H10" t="n">
-        <v>4.74</v>
+        <v>1.69</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,51 +1331,51 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>17090</v>
+        <v>2450</v>
       </c>
       <c r="K10" t="n">
-        <v>19270</v>
+        <v>2525</v>
       </c>
       <c r="L10" t="n">
-        <v>20450</v>
+        <v>2965</v>
       </c>
       <c r="M10" t="n">
-        <v>18070</v>
+        <v>2505</v>
       </c>
       <c r="N10" t="n">
-        <v>4.13</v>
+        <v>1.01</v>
       </c>
       <c r="O10" t="n">
-        <v>42852924970</v>
+        <v>74844266456</v>
       </c>
       <c r="P10" t="n">
-        <v>28600</v>
+        <v>2965</v>
       </c>
       <c r="Q10" t="n">
-        <v>11050</v>
+        <v>865</v>
       </c>
       <c r="R10" t="n">
-        <v>-34000</v>
+        <v>181000</v>
       </c>
       <c r="S10" t="n">
-        <v>9000</v>
+        <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>아틀라스 1만대 발주 및 AI 데이터센터 방열시스템 공급 계약 체결. 삼성+아틀라스 공급망 및 로봇주 중 최고 실적.</t>
+          <t>외국인 순매수세 유입 및 시간봉 차트 지지력 확인. 3000원 돌파 기대감과 함께 개인 물량 흡수 중. 긍정적 흐름.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['아틀라스', 'AI 데이터센터', '로봇주']</t>
+          <t>['외국인', '시간봉', '거래량']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,38 +1384,38 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>190510</t>
+          <t>419050</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>삼기에너지솔루션즈</t>
+          <t>나무가</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2590</v>
+        <v>18330</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+5.71%</t>
+          <t>'+7.26%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.68</v>
+        <v>0.61</v>
       </c>
       <c r="E11" t="n">
-        <v>86</v>
+        <v>122</v>
       </c>
       <c r="F11" t="n">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="G11" t="n">
-        <v>97</v>
+        <v>324</v>
       </c>
       <c r="H11" t="n">
-        <v>1.69</v>
+        <v>4.74</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,51 +1423,51 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>2450</v>
+        <v>17090</v>
       </c>
       <c r="K11" t="n">
-        <v>2525</v>
+        <v>19270</v>
       </c>
       <c r="L11" t="n">
-        <v>2965</v>
+        <v>20450</v>
       </c>
       <c r="M11" t="n">
-        <v>2505</v>
+        <v>18070</v>
       </c>
       <c r="N11" t="n">
-        <v>1.01</v>
+        <v>4.13</v>
       </c>
       <c r="O11" t="n">
-        <v>73353332936</v>
+        <v>43140270750</v>
       </c>
       <c r="P11" t="n">
-        <v>2965</v>
+        <v>28600</v>
       </c>
       <c r="Q11" t="n">
-        <v>865</v>
+        <v>11050</v>
       </c>
       <c r="R11" t="n">
-        <v>181000</v>
+        <v>-34000</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>9000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>거래량 증가 및 개인 물량 흡수 중. 3000원 돌파 기대감 및 외인 매수세 유입.</t>
+          <t>아틀라스 1만대 발주 및 AI 데이터센터 방열시스템 공급 계약 체결. 삼성+아틀라스 공급망 및 로봇주 중 최고 실적.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['거래량', '외국인', '시세 분출']</t>
+          <t>['아틀라스', 'AI 데이터센터', '로봇주']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>419050</t>
+          <t>190510</t>
         </is>
       </c>
     </row>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>181900</v>
+        <v>181800</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+4.36%</t>
+          <t>'+4.30%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>-0.06</v>
       </c>
       <c r="E12" t="n">
-        <v>534</v>
+        <v>544</v>
       </c>
       <c r="F12" t="n">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="G12" t="n">
-        <v>1766</v>
+        <v>1825</v>
       </c>
       <c r="H12" t="n">
         <v>35.43</v>
@@ -1530,7 +1530,7 @@
         <v>35.49</v>
       </c>
       <c r="O12" t="n">
-        <v>115571690950</v>
+        <v>117143583050</v>
       </c>
       <c r="P12" t="n">
         <v>304000</v>
@@ -1546,16 +1546,16 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>호재에도 불구하고 주가 상승 미미. 프로그램 매수 외에는 긍정적 모멘텀 부족 및 공매도 비율 부담.</t>
+          <t>엔비디아 지분 투자 루머에도 불구하고 주가 부진. 외국인 지분 매도 및 신한증권의 지속적인 매도세. 긍정적 재료 부재.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['공매도', '프로그램 매수', '주가 부진']</t>
+          <t>['엔비디아', '지분투자', '주가부진']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>64200</v>
+        <v>64300</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+3.22%</t>
+          <t>'+3.38%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>0.57</v>
       </c>
       <c r="E13" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="F13" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G13" t="n">
-        <v>526</v>
+        <v>541</v>
       </c>
       <c r="H13" t="n">
         <v>41.01</v>
@@ -1622,7 +1622,7 @@
         <v>40.44</v>
       </c>
       <c r="O13" t="n">
-        <v>166539903000</v>
+        <v>168642926800</v>
       </c>
       <c r="P13" t="n">
         <v>67300</v>
@@ -1638,16 +1638,16 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>자사주 매입 지속 및 코스피 수익률 1위 달성. 공매도 세력에 대한 경계와 함께 긍정적 추세 전환 기대.</t>
+          <t>최근 4일간 코스피 수익률 1위 달성. 자사주 매입 지속 및 프로그램 매수세 유입 확인. 긍정적 추세 전환 기대.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['자사주 매입', '수익률', '공매도']</t>
+          <t>['자사주매입', '프로그램매수', '수익률']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1667,70 +1667,70 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>카카오</t>
+          <t>앤로보틱스</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>30150</v>
+        <v>2235</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+2.20%</t>
+          <t>'+3.00%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.01</v>
+        <v>0.18</v>
       </c>
       <c r="E14" t="n">
-        <v>94</v>
+        <v>75</v>
       </c>
       <c r="F14" t="n">
-        <v>70</v>
+        <v>41</v>
       </c>
       <c r="G14" t="n">
-        <v>370</v>
+        <v>248</v>
       </c>
       <c r="H14" t="n">
-        <v>28.81</v>
+        <v>5.07</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>29500</v>
+        <v>2170</v>
       </c>
       <c r="K14" t="n">
-        <v>29900</v>
+        <v>2160</v>
       </c>
       <c r="L14" t="n">
-        <v>30650</v>
+        <v>2475</v>
       </c>
       <c r="M14" t="n">
-        <v>29900</v>
+        <v>2155</v>
       </c>
       <c r="N14" t="n">
-        <v>28.82</v>
+        <v>4.89</v>
       </c>
       <c r="O14" t="n">
-        <v>25869097650</v>
+        <v>45425271083</v>
       </c>
       <c r="P14" t="n">
-        <v>69700</v>
+        <v>4980</v>
       </c>
       <c r="Q14" t="n">
-        <v>29200</v>
+        <v>774</v>
       </c>
       <c r="R14" t="n">
-        <v>120000</v>
+        <v>439000</v>
       </c>
       <c r="S14" t="n">
-        <v>14000</v>
+        <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>거래량 부진 및 지속적인 하락세에 대한 불만. 공매도 및 부정적 이슈 언급. 객관적 근거 부족.</t>
+          <t>로봇 섹터 강세 속 앤로보틱스 주가 움직임에 대한 기대와 우려가 공존. 자사주 매도 및 신용 증가 등 혼조세.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,90 +1739,90 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['하락세', '공매도', '거래량']</t>
+          <t>['로봇 섹터', '신용 증가', '자사주 매도']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>035720</t>
+          <t>138360</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>앤로보틱스</t>
+          <t>카카오</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2210</v>
+        <v>30100</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+1.84%</t>
+          <t>'+2.03%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.18</v>
+        <v>-0.01</v>
       </c>
       <c r="E15" t="n">
-        <v>71</v>
+        <v>100</v>
       </c>
       <c r="F15" t="n">
-        <v>40</v>
+        <v>74</v>
       </c>
       <c r="G15" t="n">
-        <v>246</v>
+        <v>379</v>
       </c>
       <c r="H15" t="n">
-        <v>5.07</v>
+        <v>28.81</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>2170</v>
+        <v>29500</v>
       </c>
       <c r="K15" t="n">
-        <v>2160</v>
+        <v>29900</v>
       </c>
       <c r="L15" t="n">
-        <v>2475</v>
+        <v>30650</v>
       </c>
       <c r="M15" t="n">
-        <v>2155</v>
+        <v>29900</v>
       </c>
       <c r="N15" t="n">
-        <v>4.89</v>
+        <v>28.82</v>
       </c>
       <c r="O15" t="n">
-        <v>44827355373</v>
+        <v>26100455050</v>
       </c>
       <c r="P15" t="n">
-        <v>4980</v>
+        <v>69700</v>
       </c>
       <c r="Q15" t="n">
-        <v>774</v>
+        <v>29200</v>
       </c>
       <c r="R15" t="n">
-        <v>439000</v>
+        <v>120000</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>14000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>로봇 섹터 강세 속 앤로보틱스 주가 움직임에 대한 기대와 우려가 공존. 자사주 매도 및 신용 증가 등 혼조세.</t>
+          <t>거래량 부진 및 지속적인 하락세에 대한 불만. 공매도 및 부정적 이슈 언급. 객관적 근거 부족.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,20 +1831,20 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['로봇 섹터', '신용 증가', '자사주 매도']</t>
+          <t>['하락세', '공매도', '거래량']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>138360</t>
+          <t>035720</t>
         </is>
       </c>
     </row>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>16380</v>
+        <v>16400</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-0.06%</t>
+          <t>'+0.06%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F16" t="n">
         <v>72</v>
       </c>
       <c r="G16" t="n">
-        <v>281</v>
+        <v>294</v>
       </c>
       <c r="H16" t="n">
         <v>28.03</v>
@@ -1898,7 +1898,7 @@
         <v>27.96</v>
       </c>
       <c r="O16" t="n">
-        <v>34979466750</v>
+        <v>35647411930</v>
       </c>
       <c r="P16" t="n">
         <v>35350</v>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>주문량 대비 주가 부진 및 증권사 목표가 하향에 대한 불만. 실적 발표에도 주가 흐름 미미.</t>
+          <t>주문은 넘치나 주가는 지지부진. 일부 애널리스트 목표가 하향 및 증권사 불신 제기. 불확실성 존재.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['실적', '목표주가', '조선주']</t>
+          <t>['조선주', '목표주가', '실적']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1958,13 +1958,13 @@
         <v>-0.03</v>
       </c>
       <c r="E17" t="n">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="F17" t="n">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="G17" t="n">
-        <v>1031</v>
+        <v>1058</v>
       </c>
       <c r="H17" t="n">
         <v>10.31</v>
@@ -1990,7 +1990,7 @@
         <v>10.34</v>
       </c>
       <c r="O17" t="n">
-        <v>57237321200</v>
+        <v>57527112400</v>
       </c>
       <c r="P17" t="n">
         <v>154800</v>
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>14130</v>
+        <v>14100</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-2.21%</t>
+          <t>'-2.42%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>-0.19</v>
       </c>
       <c r="E18" t="n">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="F18" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="G18" t="n">
-        <v>428</v>
+        <v>438</v>
       </c>
       <c r="H18" t="n">
         <v>9.83</v>
@@ -2076,13 +2076,13 @@
         <v>14870</v>
       </c>
       <c r="M18" t="n">
-        <v>14100</v>
+        <v>14090</v>
       </c>
       <c r="N18" t="n">
         <v>10.02</v>
       </c>
       <c r="O18" t="n">
-        <v>48371926135</v>
+        <v>50207944575</v>
       </c>
       <c r="P18" t="n">
         <v>40350</v>
@@ -2098,16 +2098,16 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>코스피 지수 상승에도 불구하고 주가 하락 및 투자자 불만 고조. 경영진의 적극적인 대응 부재에 대한 비판.</t>
+          <t>코스피 지수 상승에도 불구하고 주가 하락. 경영진에 대한 불신 및 주가 조작 의혹 제기. 부정적 여론 팽배.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['주가 조작', '경영진', '상폐']</t>
+          <t>['주가조작', '경영진', '하락']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2131,11 +2131,11 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2000</v>
+        <v>2005</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-4.08%</t>
+          <t>'-3.84%</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -2148,7 +2148,7 @@
         <v>54</v>
       </c>
       <c r="G19" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H19" t="n">
         <v>2.52</v>
@@ -2174,7 +2174,7 @@
         <v>2.13</v>
       </c>
       <c r="O19" t="n">
-        <v>14108009034</v>
+        <v>14184808971</v>
       </c>
       <c r="P19" t="n">
         <v>6190</v>

--- a/data/trending_integrated_20261028_12.xlsx
+++ b/data/trending_integrated_20261028_12.xlsx
@@ -578,13 +578,13 @@
         <v>-0.19</v>
       </c>
       <c r="E2" t="n">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="F2" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G2" t="n">
-        <v>243</v>
+        <v>254</v>
       </c>
       <c r="H2" t="n">
         <v>1.2</v>
@@ -610,7 +610,7 @@
         <v>1.39</v>
       </c>
       <c r="O2" t="n">
-        <v>149982456061</v>
+        <v>150272489971</v>
       </c>
       <c r="P2" t="n">
         <v>8100</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>미국 광통신주 급등 영향 및 전고점 돌파 시도. 긍정적 차트 분석과 함께 상한가 기대감 형성. 단기 급등 가능성.</t>
+          <t>광통신주 상승세에 따른 기대감 및 차트상 상승 가능성 언급.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['광통신', '전고점', '상한가']</t>
+          <t>['광통신주', '차트 분석', '상승 가능성']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19110</v>
+        <v>18660</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+20.72%</t>
+          <t>'+17.88%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>1.02</v>
       </c>
       <c r="E3" t="n">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="F3" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="G3" t="n">
-        <v>297</v>
+        <v>309</v>
       </c>
       <c r="H3" t="n">
         <v>1.11</v>
@@ -702,7 +702,7 @@
         <v>0.09</v>
       </c>
       <c r="O3" t="n">
-        <v>265432306350</v>
+        <v>275682847025</v>
       </c>
       <c r="P3" t="n">
         <v>28800</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>미 마이크론 반도체 장비 평가 완료 및 ASML 공급망 진입 가능성. 전세계 반도체 공급망 확장 수혜 기대. 강력한 호재.</t>
+          <t>미국 마이크론 공급망 진입 뉴스 및 반도체 업황 호조에 따른 급등 기대.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['반도체장비', '공급망', '마이크론']</t>
+          <t>['마이크론 공급망', '반도체 업황', '급등 기대']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>27850</v>
+        <v>27700</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+17.26%</t>
+          <t>'+16.63%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.15</v>
       </c>
       <c r="E4" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F4" t="n">
         <v>46</v>
       </c>
       <c r="G4" t="n">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="H4" t="n">
         <v>5.16</v>
@@ -794,7 +794,7 @@
         <v>5.31</v>
       </c>
       <c r="O4" t="n">
-        <v>157250933225</v>
+        <v>159674003475</v>
       </c>
       <c r="P4" t="n">
         <v>50600</v>
@@ -843,21 +843,21 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9310</v>
+        <v>9210</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+13.54%</t>
+          <t>'+12.32%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.27</v>
       </c>
       <c r="E5" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F5" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G5" t="n">
         <v>73</v>
@@ -886,7 +886,7 @@
         <v>1.15</v>
       </c>
       <c r="O5" t="n">
-        <v>108927444625</v>
+        <v>110332767470</v>
       </c>
       <c r="P5" t="n">
         <v>9820</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>189100</v>
+        <v>190000</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+10.52%</t>
+          <t>'+11.05%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.01</v>
       </c>
       <c r="E6" t="n">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="F6" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G6" t="n">
-        <v>284</v>
+        <v>301</v>
       </c>
       <c r="H6" t="n">
         <v>74.90000000000001</v>
@@ -969,7 +969,7 @@
         <v>176300</v>
       </c>
       <c r="L6" t="n">
-        <v>189100</v>
+        <v>190100</v>
       </c>
       <c r="M6" t="n">
         <v>175400</v>
@@ -978,7 +978,7 @@
         <v>74.89</v>
       </c>
       <c r="O6" t="n">
-        <v>560048310800</v>
+        <v>584905533400</v>
       </c>
       <c r="P6" t="n">
         <v>243500</v>
@@ -1027,11 +1027,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1480000</v>
+        <v>1482000</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+10.37%</t>
+          <t>'+10.51%</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1041,10 +1041,10 @@
         <v>800</v>
       </c>
       <c r="F7" t="n">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="G7" t="n">
-        <v>1765</v>
+        <v>1706</v>
       </c>
       <c r="H7" t="n">
         <v>48.61</v>
@@ -1061,7 +1061,7 @@
         <v>1390000</v>
       </c>
       <c r="L7" t="n">
-        <v>1480000</v>
+        <v>1486000</v>
       </c>
       <c r="M7" t="n">
         <v>1358000</v>
@@ -1070,7 +1070,7 @@
         <v>48.66</v>
       </c>
       <c r="O7" t="n">
-        <v>3558667044000</v>
+        <v>3731898103000</v>
       </c>
       <c r="P7" t="n">
         <v>2987000</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>29년까지 완판 전망 및 자사주 20조 취득 발표. 반도체 업황 불신 해소 및 주가 상승 모멘텀 확보. 긍정적 전망.</t>
+          <t>4분기 실적 기대감 및 자사주 매입 소식에 따른 급등 전망.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['반도체', '업황', '자사주']</t>
+          <t>['실적 기대', '자사주 매입', '급등 전망']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,11 +1119,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>242000</v>
+        <v>242250</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+9.01%</t>
+          <t>'+9.12%</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1133,10 +1133,10 @@
         <v>800</v>
       </c>
       <c r="F8" t="n">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="G8" t="n">
-        <v>1675</v>
+        <v>1655</v>
       </c>
       <c r="H8" t="n">
         <v>46.15</v>
@@ -1162,7 +1162,7 @@
         <v>46.1</v>
       </c>
       <c r="O8" t="n">
-        <v>2395791540500</v>
+        <v>2483771892500</v>
       </c>
       <c r="P8" t="n">
         <v>374500</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>HBM4 점유율 경쟁 전망 및 증권사 목표가 상향 가능성 언급. 긍정적 기대감 존재하나 구체적 근거 부족.</t>
+          <t>노무라 증권의 목표가 제시 및 오후 자금 투입 기대감으로 상승 전망.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['HBM4', '점유율', '증권사']</t>
+          <t>['목표가', '자금 투입', '상승 전망']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14910</v>
+        <v>14920</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+8.83%</t>
+          <t>'+8.91%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>0.05</v>
       </c>
       <c r="E9" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F9" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G9" t="n">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="H9" t="n">
         <v>2.87</v>
@@ -1254,7 +1254,7 @@
         <v>2.82</v>
       </c>
       <c r="O9" t="n">
-        <v>153637971890</v>
+        <v>155188102150</v>
       </c>
       <c r="P9" t="n">
         <v>31500</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>메타 유리기판 및 해상광통신 케이블 사업 기대감. 외국인 프로그램 매수세 지속 및 공매도 세력 약화 전망. 긍정적 시세 분출 예상.</t>
+          <t>메타버스, 해상광통신 등 신규 사업 기대감 및 외국인 프로그램 매수세 유입.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['광통신', '유리기판', '외국인']</t>
+          <t>['메타버스', '해상광통신', '외국인 매수']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1314,13 +1314,13 @@
         <v>0.68</v>
       </c>
       <c r="E10" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F10" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G10" t="n">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="H10" t="n">
         <v>1.69</v>
@@ -1346,7 +1346,7 @@
         <v>1.01</v>
       </c>
       <c r="O10" t="n">
-        <v>74844266456</v>
+        <v>77082325894</v>
       </c>
       <c r="P10" t="n">
         <v>2965</v>
@@ -1362,16 +1362,16 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>외국인 순매수세 유입 및 시간봉 차트 지지력 확인. 3000원 돌파 기대감과 함께 개인 물량 흡수 중. 긍정적 흐름.</t>
+          <t>거래량 증가 및 외국인 매수세 유입에 따른 주가 반등 기대.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['외국인', '시간봉', '거래량']</t>
+          <t>['거래량 증가', '외국인 매수', '주가 반등']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>18330</v>
+        <v>18230</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+7.26%</t>
+          <t>'+6.67%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.61</v>
       </c>
       <c r="E11" t="n">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="F11" t="n">
         <v>64</v>
       </c>
       <c r="G11" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H11" t="n">
         <v>4.74</v>
@@ -1438,7 +1438,7 @@
         <v>4.13</v>
       </c>
       <c r="O11" t="n">
-        <v>43140270750</v>
+        <v>43791429385</v>
       </c>
       <c r="P11" t="n">
         <v>28600</v>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>181800</v>
+        <v>181500</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+4.30%</t>
+          <t>'+4.13%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>-0.06</v>
       </c>
       <c r="E12" t="n">
-        <v>544</v>
+        <v>566</v>
       </c>
       <c r="F12" t="n">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="G12" t="n">
-        <v>1825</v>
+        <v>1897</v>
       </c>
       <c r="H12" t="n">
         <v>35.43</v>
@@ -1530,7 +1530,7 @@
         <v>35.49</v>
       </c>
       <c r="O12" t="n">
-        <v>117143583050</v>
+        <v>119573118000</v>
       </c>
       <c r="P12" t="n">
         <v>304000</v>
@@ -1546,16 +1546,16 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>엔비디아 지분 투자 루머에도 불구하고 주가 부진. 외국인 지분 매도 및 신한증권의 지속적인 매도세. 긍정적 재료 부재.</t>
+          <t>엔비디아의 지분 투자에도 불구하고 신한증권의 매도세 및 주가 부진.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['엔비디아', '지분투자', '주가부진']</t>
+          <t>['엔비디아 투자', '신한 매도', '주가 부진']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1590,13 +1590,13 @@
         <v>0.57</v>
       </c>
       <c r="E13" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F13" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G13" t="n">
-        <v>541</v>
+        <v>552</v>
       </c>
       <c r="H13" t="n">
         <v>41.01</v>
@@ -1622,7 +1622,7 @@
         <v>40.44</v>
       </c>
       <c r="O13" t="n">
-        <v>168642926800</v>
+        <v>172197298250</v>
       </c>
       <c r="P13" t="n">
         <v>67300</v>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2235</v>
+        <v>2225</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+3.00%</t>
+          <t>'+2.53%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0.18</v>
       </c>
       <c r="E14" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F14" t="n">
         <v>41</v>
       </c>
       <c r="G14" t="n">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H14" t="n">
         <v>5.07</v>
@@ -1714,7 +1714,7 @@
         <v>4.89</v>
       </c>
       <c r="O14" t="n">
-        <v>45425271083</v>
+        <v>45912539378</v>
       </c>
       <c r="P14" t="n">
         <v>4980</v>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>30100</v>
+        <v>30050</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+2.03%</t>
+          <t>'+1.86%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-0.01</v>
       </c>
       <c r="E15" t="n">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="F15" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G15" t="n">
-        <v>379</v>
+        <v>388</v>
       </c>
       <c r="H15" t="n">
         <v>28.81</v>
@@ -1806,7 +1806,7 @@
         <v>28.82</v>
       </c>
       <c r="O15" t="n">
-        <v>26100455050</v>
+        <v>26797490400</v>
       </c>
       <c r="P15" t="n">
         <v>69700</v>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>16400</v>
+        <v>16430</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'+0.06%</t>
+          <t>'+0.24%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="F16" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G16" t="n">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="H16" t="n">
         <v>28.03</v>
@@ -1898,7 +1898,7 @@
         <v>27.96</v>
       </c>
       <c r="O16" t="n">
-        <v>35647411930</v>
+        <v>36839372835</v>
       </c>
       <c r="P16" t="n">
         <v>35350</v>
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>52100</v>
+        <v>52300</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-1.70%</t>
+          <t>'-1.32%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>-0.03</v>
       </c>
       <c r="E17" t="n">
-        <v>372</v>
+        <v>382</v>
       </c>
       <c r="F17" t="n">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="G17" t="n">
-        <v>1058</v>
+        <v>1095</v>
       </c>
       <c r="H17" t="n">
         <v>10.31</v>
@@ -1990,7 +1990,7 @@
         <v>10.34</v>
       </c>
       <c r="O17" t="n">
-        <v>57527112400</v>
+        <v>61734522650</v>
       </c>
       <c r="P17" t="n">
         <v>154800</v>
@@ -2006,7 +2006,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>코스피 지수 상승 속에서도 주가 하락 지속. 미국 조선업 협력 난항 및 부정적인 시장 전망.</t>
+          <t>실적 발표 및 외국인 매도세 속에서도 잠수함 건조 제안 등 일부 긍정적 뉴스.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['잠수함', '조선업', '미국 해군']</t>
+          <t>['실적 발표', '외국인 매도', '잠수함 건조']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>14100</v>
+        <v>14170</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-2.42%</t>
+          <t>'-1.94%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>-0.19</v>
       </c>
       <c r="E18" t="n">
-        <v>213</v>
+        <v>225</v>
       </c>
       <c r="F18" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="G18" t="n">
-        <v>438</v>
+        <v>456</v>
       </c>
       <c r="H18" t="n">
         <v>9.83</v>
@@ -2082,7 +2082,7 @@
         <v>10.02</v>
       </c>
       <c r="O18" t="n">
-        <v>50207944575</v>
+        <v>51095611055</v>
       </c>
       <c r="P18" t="n">
         <v>40350</v>
@@ -2098,16 +2098,16 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>코스피 지수 상승에도 불구하고 주가 하락. 경영진에 대한 불신 및 주가 조작 의혹 제기. 부정적 여론 팽배.</t>
+          <t>코스피 지수 상승에도 불구하고 주가 하락 및 경영진에 대한 불신.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['주가조작', '경영진', '하락']</t>
+          <t>['주가 하락', '경영진 불신', '개잡주']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2131,18 +2131,18 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2005</v>
+        <v>1997</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-3.84%</t>
+          <t>'-4.22%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>0.39</v>
       </c>
       <c r="E19" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F19" t="n">
         <v>54</v>
@@ -2174,7 +2174,7 @@
         <v>2.13</v>
       </c>
       <c r="O19" t="n">
-        <v>14184808971</v>
+        <v>14396625716</v>
       </c>
       <c r="P19" t="n">
         <v>6190</v>

--- a/data/trending_integrated_20261028_12.xlsx
+++ b/data/trending_integrated_20261028_12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z19"/>
+  <dimension ref="A1:Z20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,13 +578,13 @@
         <v>-0.19</v>
       </c>
       <c r="E2" t="n">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="F2" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G2" t="n">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="H2" t="n">
         <v>1.2</v>
@@ -610,7 +610,7 @@
         <v>1.39</v>
       </c>
       <c r="O2" t="n">
-        <v>150272489971</v>
+        <v>150416516906</v>
       </c>
       <c r="P2" t="n">
         <v>8100</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>광통신주 상승세에 따른 기대감 및 차트상 상승 가능성 언급.</t>
+          <t>빛과전자, 급등세 기록하며 연상 기대감 형성. 과거 쓰레기 회사 이미지 탈피 및 주가 상승 여력 주목.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['광통신주', '차트 분석', '상승 가능성']</t>
+          <t>['급등', '차트']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18660</v>
+        <v>18770</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+17.88%</t>
+          <t>'+18.57%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>1.02</v>
       </c>
       <c r="E3" t="n">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="F3" t="n">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="G3" t="n">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="H3" t="n">
         <v>1.11</v>
@@ -702,7 +702,7 @@
         <v>0.09</v>
       </c>
       <c r="O3" t="n">
-        <v>275682847025</v>
+        <v>279521934575</v>
       </c>
       <c r="P3" t="n">
         <v>28800</v>
@@ -718,7 +718,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>미국 마이크론 공급망 진입 뉴스 및 반도체 업황 호조에 따른 급등 기대.</t>
+          <t>멜콘, 마이크론 반도체 장비 평가 완료 및 ASML 공급망 진입 기대. 3조 밸류에이션 주장 및 10만 멜콘 목표.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['마이크론 공급망', '반도체 업황', '급등 기대']</t>
+          <t>['반도체 장비', '공급망']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>27700</v>
+        <v>27900</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+16.63%</t>
+          <t>'+17.47%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.15</v>
       </c>
       <c r="E4" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F4" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G4" t="n">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="H4" t="n">
         <v>5.16</v>
@@ -794,7 +794,7 @@
         <v>5.31</v>
       </c>
       <c r="O4" t="n">
-        <v>159674003475</v>
+        <v>161567896225</v>
       </c>
       <c r="P4" t="n">
         <v>50600</v>
@@ -839,79 +839,79 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>샌즈랩</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9210</v>
+        <v>189700</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+12.32%</t>
+          <t>'+10.87%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.27</v>
+        <v>0.01</v>
       </c>
       <c r="E5" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F5" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G5" t="n">
-        <v>73</v>
+        <v>316</v>
       </c>
       <c r="H5" t="n">
-        <v>1.42</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>8200</v>
+        <v>171100</v>
       </c>
       <c r="K5" t="n">
-        <v>8230</v>
+        <v>176300</v>
       </c>
       <c r="L5" t="n">
-        <v>9780</v>
+        <v>190100</v>
       </c>
       <c r="M5" t="n">
-        <v>8100</v>
+        <v>175400</v>
       </c>
       <c r="N5" t="n">
-        <v>1.15</v>
+        <v>74.89</v>
       </c>
       <c r="O5" t="n">
-        <v>110332767470</v>
+        <v>593681819150</v>
       </c>
       <c r="P5" t="n">
-        <v>9820</v>
+        <v>243500</v>
       </c>
       <c r="Q5" t="n">
-        <v>2965</v>
+        <v>71000</v>
       </c>
       <c r="R5" t="n">
-        <v>-63000</v>
+        <v>654000</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>-1000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>샌즈랩, 미국 양자컴퓨터 및 보안주 강세와 국내 IT 보안 사고 뉴스에 따른 관심 증가. AI 시대 보안 중요성 부각.</t>
+          <t>삼성전자우, 숏 스퀴즈 기대감 및 실적 발표 중요성 부각. 배당 및 자사주 매입 관련 논의.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['AI 보안', '양자컴퓨터', 'IT 보안']</t>
+          <t>['실적 발표', '자사주 매입']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -919,43 +919,43 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>411080</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>190000</v>
+        <v>1485000</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+11.05%</t>
+          <t>'+10.74%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.01</v>
+        <v>-0.05</v>
       </c>
       <c r="E6" t="n">
-        <v>75</v>
+        <v>800</v>
       </c>
       <c r="F6" t="n">
-        <v>57</v>
+        <v>525</v>
       </c>
       <c r="G6" t="n">
-        <v>301</v>
+        <v>1685</v>
       </c>
       <c r="H6" t="n">
-        <v>74.90000000000001</v>
+        <v>48.61</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,152 +963,152 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>171100</v>
+        <v>1341000</v>
       </c>
       <c r="K6" t="n">
-        <v>176300</v>
+        <v>1390000</v>
       </c>
       <c r="L6" t="n">
-        <v>190100</v>
+        <v>1488000</v>
       </c>
       <c r="M6" t="n">
-        <v>175400</v>
+        <v>1358000</v>
       </c>
       <c r="N6" t="n">
-        <v>74.89</v>
+        <v>48.66</v>
       </c>
       <c r="O6" t="n">
-        <v>584905533400</v>
+        <v>3810314842500</v>
       </c>
       <c r="P6" t="n">
-        <v>243500</v>
+        <v>2987000</v>
       </c>
       <c r="Q6" t="n">
-        <v>71000</v>
+        <v>501000</v>
       </c>
       <c r="R6" t="n">
-        <v>654000</v>
+        <v>53000</v>
       </c>
       <c r="S6" t="n">
-        <v>-1000</v>
+        <v>55000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>삼성전자우, 외국인 매수세 및 숏 스퀴즈 가능성 언급. 자사주 매입 기대.</t>
+          <t>SK하이닉스, 4분기 실적 기대감 및 자사주 20조 취득 발표. 목표 주가 상향 조정.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['숏 스퀴즈', '자사주매입', '우선주']</t>
+          <t>['실적', '자사주']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>샌즈랩</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1482000</v>
+        <v>9020</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+10.51%</t>
+          <t>'+10.00%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.05</v>
+        <v>0.27</v>
       </c>
       <c r="E7" t="n">
-        <v>800</v>
+        <v>79</v>
       </c>
       <c r="F7" t="n">
-        <v>526</v>
+        <v>61</v>
       </c>
       <c r="G7" t="n">
-        <v>1706</v>
+        <v>75</v>
       </c>
       <c r="H7" t="n">
-        <v>48.61</v>
+        <v>1.42</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>1341000</v>
+        <v>8200</v>
       </c>
       <c r="K7" t="n">
-        <v>1390000</v>
+        <v>8230</v>
       </c>
       <c r="L7" t="n">
-        <v>1486000</v>
+        <v>9780</v>
       </c>
       <c r="M7" t="n">
-        <v>1358000</v>
+        <v>8100</v>
       </c>
       <c r="N7" t="n">
-        <v>48.66</v>
+        <v>1.15</v>
       </c>
       <c r="O7" t="n">
-        <v>3731898103000</v>
+        <v>112784779150</v>
       </c>
       <c r="P7" t="n">
-        <v>2987000</v>
+        <v>9820</v>
       </c>
       <c r="Q7" t="n">
-        <v>501000</v>
+        <v>2965</v>
       </c>
       <c r="R7" t="n">
-        <v>53000</v>
+        <v>-63000</v>
       </c>
       <c r="S7" t="n">
-        <v>55000</v>
+        <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>4분기 실적 기대감 및 자사주 매입 소식에 따른 급등 전망.</t>
+          <t>샌즈랩, 미국 양자컴퓨터 및 보안주 강세와 국내 IT 보안 사고 뉴스에 따른 관심 증가. AI 시대 보안 중요성 부각.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['실적 기대', '자사주 매입', '급등 전망']</t>
+          <t>['AI 보안', '양자컴퓨터', 'IT 보안']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>411080</t>
         </is>
       </c>
     </row>
@@ -1133,10 +1133,10 @@
         <v>800</v>
       </c>
       <c r="F8" t="n">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="G8" t="n">
-        <v>1655</v>
+        <v>1711</v>
       </c>
       <c r="H8" t="n">
         <v>46.15</v>
@@ -1162,7 +1162,7 @@
         <v>46.1</v>
       </c>
       <c r="O8" t="n">
-        <v>2483771892500</v>
+        <v>2535109469750</v>
       </c>
       <c r="P8" t="n">
         <v>374500</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>노무라 증권의 목표가 제시 및 오후 자금 투입 기대감으로 상승 전망.</t>
+          <t>삼성전자, 긍정적 전망과 함께 매수세 유입 기대. 주가 100만 전자 가능성 제기.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['목표가', '자금 투입', '상승 전망']</t>
+          <t>['실적', '전망']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14920</v>
+        <v>14930</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+8.91%</t>
+          <t>'+8.98%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>0.05</v>
       </c>
       <c r="E9" t="n">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="F9" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G9" t="n">
-        <v>524</v>
+        <v>544</v>
       </c>
       <c r="H9" t="n">
         <v>2.87</v>
@@ -1254,7 +1254,7 @@
         <v>2.82</v>
       </c>
       <c r="O9" t="n">
-        <v>155188102150</v>
+        <v>156290081980</v>
       </c>
       <c r="P9" t="n">
         <v>31500</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>메타버스, 해상광통신 등 신규 사업 기대감 및 외국인 프로그램 매수세 유입.</t>
+          <t>대한광통신, 메타 유리 기판 및 해상 광통신 케이블 관련 성장 기대. 외인 프로그램 매수 집중.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['메타버스', '해상광통신', '외국인 매수']</t>
+          <t>['광통신', '외국인 매수']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1299,31 +1299,31 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>삼기에너지솔루션즈</t>
+          <t>나무가</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2635</v>
+        <v>18390</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+7.55%</t>
+          <t>'+7.61%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.68</v>
+        <v>0.61</v>
       </c>
       <c r="E10" t="n">
-        <v>89</v>
+        <v>129</v>
       </c>
       <c r="F10" t="n">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="G10" t="n">
-        <v>105</v>
+        <v>334</v>
       </c>
       <c r="H10" t="n">
-        <v>1.69</v>
+        <v>4.74</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,51 +1331,51 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>2450</v>
+        <v>17090</v>
       </c>
       <c r="K10" t="n">
-        <v>2525</v>
+        <v>19270</v>
       </c>
       <c r="L10" t="n">
-        <v>2965</v>
+        <v>20450</v>
       </c>
       <c r="M10" t="n">
-        <v>2505</v>
+        <v>18070</v>
       </c>
       <c r="N10" t="n">
-        <v>1.01</v>
+        <v>4.13</v>
       </c>
       <c r="O10" t="n">
-        <v>77082325894</v>
+        <v>44203515045</v>
       </c>
       <c r="P10" t="n">
-        <v>2965</v>
+        <v>28600</v>
       </c>
       <c r="Q10" t="n">
-        <v>865</v>
+        <v>11050</v>
       </c>
       <c r="R10" t="n">
-        <v>181000</v>
+        <v>-34000</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>9000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>거래량 증가 및 외국인 매수세 유입에 따른 주가 반등 기대.</t>
+          <t>아틀라스 1만대 발주 및 AI 데이터센터 방열시스템 공급 계약 체결. 삼성+아틀라스 공급망 및 로봇주 중 최고 실적.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['거래량 증가', '외국인 매수', '주가 반등']</t>
+          <t>['아틀라스', 'AI 데이터센터', '로봇주']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,38 +1384,38 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>419050</t>
+          <t>190510</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>나무가</t>
+          <t>삼기에너지솔루션즈</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>18230</v>
+        <v>2625</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+6.67%</t>
+          <t>'+7.14%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.61</v>
+        <v>0.68</v>
       </c>
       <c r="E11" t="n">
-        <v>127</v>
+        <v>89</v>
       </c>
       <c r="F11" t="n">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="G11" t="n">
-        <v>325</v>
+        <v>106</v>
       </c>
       <c r="H11" t="n">
-        <v>4.74</v>
+        <v>1.69</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,51 +1423,51 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>17090</v>
+        <v>2450</v>
       </c>
       <c r="K11" t="n">
-        <v>19270</v>
+        <v>2525</v>
       </c>
       <c r="L11" t="n">
-        <v>20450</v>
+        <v>2965</v>
       </c>
       <c r="M11" t="n">
-        <v>18070</v>
+        <v>2505</v>
       </c>
       <c r="N11" t="n">
-        <v>4.13</v>
+        <v>1.01</v>
       </c>
       <c r="O11" t="n">
-        <v>43791429385</v>
+        <v>77806710326</v>
       </c>
       <c r="P11" t="n">
-        <v>28600</v>
+        <v>2965</v>
       </c>
       <c r="Q11" t="n">
-        <v>11050</v>
+        <v>865</v>
       </c>
       <c r="R11" t="n">
-        <v>-34000</v>
+        <v>181000</v>
       </c>
       <c r="S11" t="n">
-        <v>9000</v>
+        <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>아틀라스 1만대 발주 및 AI 데이터센터 방열시스템 공급 계약 체결. 삼성+아틀라스 공급망 및 로봇주 중 최고 실적.</t>
+          <t>삼기에너지솔루션즈, 거래량 증가 속 개인 물량 흡수 및 반등 기대. 전환사채 발행 이슈.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['아틀라스', 'AI 데이터센터', '로봇주']</t>
+          <t>['거래량', '전환사채']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>190510</t>
+          <t>419050</t>
         </is>
       </c>
     </row>
@@ -1498,13 +1498,13 @@
         <v>-0.06</v>
       </c>
       <c r="E12" t="n">
-        <v>566</v>
+        <v>580</v>
       </c>
       <c r="F12" t="n">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="G12" t="n">
-        <v>1897</v>
+        <v>1965</v>
       </c>
       <c r="H12" t="n">
         <v>35.43</v>
@@ -1530,7 +1530,7 @@
         <v>35.49</v>
       </c>
       <c r="O12" t="n">
-        <v>119573118000</v>
+        <v>121059933850</v>
       </c>
       <c r="P12" t="n">
         <v>304000</v>
@@ -1546,16 +1546,16 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>엔비디아의 지분 투자에도 불구하고 신한증권의 매도세 및 주가 부진.</t>
+          <t>프로그램 매수 의존적 흐름과 외인/연기금 매도세에 대한 부정적 전망. 엔비디아 지분 투자에도 불구하고 주가 부진.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['엔비디아 투자', '신한 매도', '주가 부진']</t>
+          <t>['프로그램 매수', '외인 매도', '엔비디아']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1590,13 +1590,13 @@
         <v>0.57</v>
       </c>
       <c r="E13" t="n">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="F13" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G13" t="n">
-        <v>552</v>
+        <v>591</v>
       </c>
       <c r="H13" t="n">
         <v>41.01</v>
@@ -1622,7 +1622,7 @@
         <v>40.44</v>
       </c>
       <c r="O13" t="n">
-        <v>172197298250</v>
+        <v>174731821050</v>
       </c>
       <c r="P13" t="n">
         <v>67300</v>
@@ -1638,16 +1638,16 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>최근 4일간 코스피 수익률 1위 달성. 자사주 매입 지속 및 프로그램 매수세 유입 확인. 긍정적 추세 전환 기대.</t>
+          <t>삼성E&amp;A, 높은 수익률 달성 및 귀족주 편입 전망. 공매도 세력과의 대립 및 자사주 매입 효과 기대.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['자사주매입', '프로그램매수', '수익률']</t>
+          <t>['자사주 매입', '공매도']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1688,7 +1688,7 @@
         <v>41</v>
       </c>
       <c r="G14" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H14" t="n">
         <v>5.07</v>
@@ -1714,7 +1714,7 @@
         <v>4.89</v>
       </c>
       <c r="O14" t="n">
-        <v>45912539378</v>
+        <v>46212942900</v>
       </c>
       <c r="P14" t="n">
         <v>4980</v>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>30050</v>
+        <v>30100</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+1.86%</t>
+          <t>'+2.03%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-0.01</v>
       </c>
       <c r="E15" t="n">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="F15" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G15" t="n">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="H15" t="n">
         <v>28.81</v>
@@ -1806,7 +1806,7 @@
         <v>28.82</v>
       </c>
       <c r="O15" t="n">
-        <v>26797490400</v>
+        <v>27359720875</v>
       </c>
       <c r="P15" t="n">
         <v>69700</v>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>16430</v>
+        <v>16440</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'+0.24%</t>
+          <t>'+0.31%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F16" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G16" t="n">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="H16" t="n">
         <v>28.03</v>
@@ -1898,7 +1898,7 @@
         <v>27.96</v>
       </c>
       <c r="O16" t="n">
-        <v>36839372835</v>
+        <v>38061101955</v>
       </c>
       <c r="P16" t="n">
         <v>35350</v>
@@ -1914,16 +1914,16 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>주문은 넘치나 주가는 지지부진. 일부 애널리스트 목표가 하향 및 증권사 불신 제기. 불확실성 존재.</t>
+          <t>삼성중공업, 주문량 대비 주가 흐름에 대한 불만 제기. 실적 발표 및 외국인/기관 매수세 지속.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['조선주', '목표주가', '실적']</t>
+          <t>['실적', '외국인 매수']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1958,13 +1958,13 @@
         <v>-0.03</v>
       </c>
       <c r="E17" t="n">
-        <v>382</v>
+        <v>391</v>
       </c>
       <c r="F17" t="n">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="G17" t="n">
-        <v>1095</v>
+        <v>1110</v>
       </c>
       <c r="H17" t="n">
         <v>10.31</v>
@@ -1990,7 +1990,7 @@
         <v>10.34</v>
       </c>
       <c r="O17" t="n">
-        <v>61734522650</v>
+        <v>62577860450</v>
       </c>
       <c r="P17" t="n">
         <v>154800</v>
@@ -2050,13 +2050,13 @@
         <v>-0.19</v>
       </c>
       <c r="E18" t="n">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="F18" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G18" t="n">
-        <v>456</v>
+        <v>463</v>
       </c>
       <c r="H18" t="n">
         <v>9.83</v>
@@ -2082,7 +2082,7 @@
         <v>10.02</v>
       </c>
       <c r="O18" t="n">
-        <v>51095611055</v>
+        <v>51866265060</v>
       </c>
       <c r="P18" t="n">
         <v>40350</v>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>코스피 지수 상승에도 불구하고 주가 하락 및 경영진에 대한 불신.</t>
+          <t>대우건설, 부정적 여론 속 상장폐지 우려 제기. 경영진 및 주가 조작 의혹.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['주가 하락', '경영진 불신', '개잡주']</t>
+          <t>['주가 조작', '경영진']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1997</v>
+        <v>2005</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-4.22%</t>
+          <t>'-3.84%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>0.39</v>
       </c>
       <c r="E19" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F19" t="n">
         <v>54</v>
       </c>
       <c r="G19" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H19" t="n">
         <v>2.52</v>
@@ -2174,7 +2174,7 @@
         <v>2.13</v>
       </c>
       <c r="O19" t="n">
-        <v>14396625716</v>
+        <v>14524247473</v>
       </c>
       <c r="P19" t="n">
         <v>6190</v>
@@ -2213,6 +2213,98 @@
       <c r="Z19" t="inlineStr">
         <is>
           <t>001510</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>HT로보틱스</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>8970</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>'-5.88%</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="E20" t="n">
+        <v>81</v>
+      </c>
+      <c r="F20" t="n">
+        <v>49</v>
+      </c>
+      <c r="G20" t="n">
+        <v>283</v>
+      </c>
+      <c r="H20" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>9530</v>
+      </c>
+      <c r="K20" t="n">
+        <v>9560</v>
+      </c>
+      <c r="L20" t="n">
+        <v>9850</v>
+      </c>
+      <c r="M20" t="n">
+        <v>8870</v>
+      </c>
+      <c r="N20" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="O20" t="n">
+        <v>39782207725</v>
+      </c>
+      <c r="P20" t="n">
+        <v>11690</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2270</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>-28000</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>하락 추세 및 8000원 목표가 전망. 매수 타이밍에 대한 부정적 의견.</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>['하락 추세', '목표가', '매수 타이밍']</t>
+        </is>
+      </c>
+      <c r="X20" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>396300</t>
         </is>
       </c>
     </row>
